--- a/supporting_material/experiments/pure-del/lane-1.xlsx
+++ b/supporting_material/experiments/pure-del/lane-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/supporting_material/experiments/pure-del/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BF47AC-8988-A84E-B595-B517A690A47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A4FD66-3935-AD45-BF46-6248DE723429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="24100" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="experiment" sheetId="8" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="271">
   <si>
     <t>CuAAC</t>
   </si>
@@ -702,6 +702,162 @@
   </si>
   <si>
     <t>lane-1</t>
+  </si>
+  <si>
+    <t>MK_25</t>
+  </si>
+  <si>
+    <t>MK_26</t>
+  </si>
+  <si>
+    <t>MK_27</t>
+  </si>
+  <si>
+    <t>MK_28</t>
+  </si>
+  <si>
+    <t>MK_29</t>
+  </si>
+  <si>
+    <t>MK_30</t>
+  </si>
+  <si>
+    <t>MK_31</t>
+  </si>
+  <si>
+    <t>MK_32</t>
+  </si>
+  <si>
+    <t>MK_33</t>
+  </si>
+  <si>
+    <t>MK_34</t>
+  </si>
+  <si>
+    <t>MK_35</t>
+  </si>
+  <si>
+    <t>MK_36</t>
+  </si>
+  <si>
+    <t>MK_37</t>
+  </si>
+  <si>
+    <t>MK_38</t>
+  </si>
+  <si>
+    <t>MK_39</t>
+  </si>
+  <si>
+    <t>MK_40</t>
+  </si>
+  <si>
+    <t>MK_41</t>
+  </si>
+  <si>
+    <t>MK_42</t>
+  </si>
+  <si>
+    <t>MK_43</t>
+  </si>
+  <si>
+    <t>MK_44</t>
+  </si>
+  <si>
+    <t>MK_45</t>
+  </si>
+  <si>
+    <t>MK_46</t>
+  </si>
+  <si>
+    <t>MK_47</t>
+  </si>
+  <si>
+    <t>MK_48</t>
+  </si>
+  <si>
+    <t>MK_49</t>
+  </si>
+  <si>
+    <t>MK_50</t>
+  </si>
+  <si>
+    <t>MK_51</t>
+  </si>
+  <si>
+    <t>alternative_name</t>
+  </si>
+  <si>
+    <t>MK_1</t>
+  </si>
+  <si>
+    <t>MK_2</t>
+  </si>
+  <si>
+    <t>MK_3</t>
+  </si>
+  <si>
+    <t>MK_4</t>
+  </si>
+  <si>
+    <t>MK_5</t>
+  </si>
+  <si>
+    <t>MK_6</t>
+  </si>
+  <si>
+    <t>MK_7</t>
+  </si>
+  <si>
+    <t>MK_8</t>
+  </si>
+  <si>
+    <t>MK_9</t>
+  </si>
+  <si>
+    <t>MK_10</t>
+  </si>
+  <si>
+    <t>MK_11</t>
+  </si>
+  <si>
+    <t>MK_12</t>
+  </si>
+  <si>
+    <t>MK_13</t>
+  </si>
+  <si>
+    <t>MK_14</t>
+  </si>
+  <si>
+    <t>MK_15</t>
+  </si>
+  <si>
+    <t>MK_16</t>
+  </si>
+  <si>
+    <t>MK_17</t>
+  </si>
+  <si>
+    <t>MK_18</t>
+  </si>
+  <si>
+    <t>MK_19</t>
+  </si>
+  <si>
+    <t>MK_20</t>
+  </si>
+  <si>
+    <t>MK_21</t>
+  </si>
+  <si>
+    <t>MK_22</t>
+  </si>
+  <si>
+    <t>MK_23</t>
+  </si>
+  <si>
+    <t>MK_24</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1282,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1273,6 +1429,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1608,1350 +1767,1507 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9286309-5176-CB48-AB9B-E8EF56CF21B1}">
-  <dimension ref="A1:H393"/>
+  <dimension ref="A1:I393"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="46" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.1640625" style="46" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" style="46" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="46" customWidth="1"/>
-    <col min="6" max="6" width="44" style="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.1640625" style="46" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.83203125" style="46"/>
+    <col min="5" max="5" width="18.33203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10" style="46" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" style="46" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4" style="46" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="12.83203125" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="D1" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="E1" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="F1" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="G1" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="H1" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="I1" s="42" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D2" s="47" t="s">
+      <c r="B2" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E2" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="F2" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="G2" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="H2" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="I2" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D3" s="47" t="s">
+      <c r="B3" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E3" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="F3" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="G3" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="H3" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="I3" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E4" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="F4" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="G4" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="H4" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="I4" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D5" s="47" t="s">
+      <c r="B5" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E5" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="F5" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="49" t="s">
+      <c r="G5" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="H5" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="I5" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D6" s="47" t="s">
+      <c r="B6" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E6" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="F6" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="G6" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="H6" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="I6" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D7" s="47" t="s">
+      <c r="B7" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E7" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="F7" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="G7" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="H7" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="I7" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D8" s="65" t="s">
+      <c r="B8" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E8" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="F8" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="G8" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="H8" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="I8" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D9" s="65" t="s">
+      <c r="B9" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E9" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="F9" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="49" t="s">
+      <c r="G9" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="42" t="s">
+      <c r="H9" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="I9" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="64" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D10" s="65" t="s">
+      <c r="B10" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E10" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="F10" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="G10" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="H10" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="I10" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D11" s="65" t="s">
+      <c r="B11" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="F11" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="G11" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="H11" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="I11" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="64" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D12" s="65" t="s">
+      <c r="B12" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E12" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="F12" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="G12" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="H12" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="I12" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="64" t="s">
         <v>177</v>
       </c>
-      <c r="B13" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D13" s="65" t="s">
+      <c r="B13" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E13" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="F13" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="49" t="s">
+      <c r="G13" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="H13" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="I13" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D14" s="47" t="s">
+      <c r="B14" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E14" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="F14" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="G14" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="H14" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="I14" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D15" s="47" t="s">
+      <c r="B15" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E15" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="F15" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="G15" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="H15" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="I15" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="B16" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D16" s="47" t="s">
+      <c r="B16" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E16" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="F16" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="48" t="s">
+      <c r="G16" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="42" t="s">
+      <c r="H16" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="I16" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D17" s="47" t="s">
+      <c r="B17" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E17" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="F17" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="G17" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="H17" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="41" t="s">
+      <c r="I17" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="64" t="s">
         <v>182</v>
       </c>
-      <c r="B18" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D18" s="47" t="s">
+      <c r="B18" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E18" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="F18" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="48" t="s">
+      <c r="G18" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="H18" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="41" t="s">
+      <c r="I18" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="B19" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D19" s="47" t="s">
+      <c r="B19" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E19" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="F19" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="G19" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="H19" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="I19" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D20" s="65" t="s">
+      <c r="B20" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E20" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="F20" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="48" t="s">
+      <c r="G20" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="H20" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="41" t="s">
+      <c r="I20" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D21" s="65" t="s">
+      <c r="B21" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E21" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="F21" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="G21" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="H21" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="41" t="s">
+      <c r="I21" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="B22" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D22" s="65" t="s">
+      <c r="B22" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E22" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="F22" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="G22" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="42" t="s">
+      <c r="H22" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="41" t="s">
+      <c r="I22" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="B23" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D23" s="47" t="s">
+      <c r="B23" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E23" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="F23" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="64"/>
+      <c r="H23" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="I23" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="B24" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D24" s="47" t="s">
+      <c r="B24" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E24" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="51" t="s">
+      <c r="F24" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64" t="s">
+      <c r="G24" s="64"/>
+      <c r="H24" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="I24" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D25" s="47" t="s">
+      <c r="B25" s="47" t="s">
+        <v>242</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E25" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="F25" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="64"/>
+      <c r="H25" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="I25" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="B26" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D26" s="47" t="s">
+      <c r="B26" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="F26" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="64"/>
+      <c r="H26" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="41" t="s">
+      <c r="I26" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="B27" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D27" s="47" t="s">
+      <c r="B27" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E27" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="F27" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64" t="s">
+      <c r="G27" s="64"/>
+      <c r="H27" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="I27" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="64" t="s">
         <v>192</v>
       </c>
-      <c r="B28" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D28" s="47" t="s">
+      <c r="B28" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E28" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="F28" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="64"/>
+      <c r="H28" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="H28" s="41" t="s">
+      <c r="I28" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="B29" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D29" s="47" t="s">
+      <c r="B29" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E29" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="F29" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="G29" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G29" s="42" t="s">
+      <c r="H29" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="66" t="s">
+      <c r="I29" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="64" t="s">
         <v>194</v>
       </c>
-      <c r="B30" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D30" s="47" t="s">
+      <c r="B30" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E30" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="F30" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="G30" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G30" s="42" t="s">
+      <c r="H30" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="66" t="s">
+      <c r="I30" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D31" s="47" t="s">
+      <c r="B31" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E31" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="E31" s="43" t="s">
+      <c r="F31" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="G31" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G31" s="42" t="s">
+      <c r="H31" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="66" t="s">
+      <c r="I31" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="64" t="s">
         <v>196</v>
       </c>
-      <c r="B32" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D32" s="47" t="s">
+      <c r="B32" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E32" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="E32" s="43" t="s">
+      <c r="F32" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="G32" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G32" s="42" t="s">
+      <c r="H32" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="66" t="s">
+      <c r="I32" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D33" s="47" t="s">
+      <c r="B33" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E33" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="E33" s="43" t="s">
+      <c r="F33" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="G33" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G33" s="42" t="s">
+      <c r="H33" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="H33" s="66" t="s">
+      <c r="I33" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D34" s="47" t="s">
+      <c r="B34" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E34" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="F34" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="G34" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G34" s="42" t="s">
+      <c r="H34" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="66" t="s">
+      <c r="I34" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="B35" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D35" s="65" t="s">
+      <c r="B35" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E35" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="F35" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="G35" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G35" s="42" t="s">
+      <c r="H35" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="H35" s="66" t="s">
+      <c r="I35" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="64" t="s">
         <v>200</v>
       </c>
-      <c r="B36" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D36" s="65" t="s">
+      <c r="B36" s="47" t="s">
+        <v>254</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E36" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="E36" s="43" t="s">
+      <c r="F36" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F36" s="49" t="s">
+      <c r="G36" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="42" t="s">
+      <c r="H36" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="66" t="s">
+      <c r="I36" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="B37" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D37" s="65" t="s">
+      <c r="B37" s="47" t="s">
+        <v>255</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E37" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="E37" s="43" t="s">
+      <c r="F37" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="G37" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G37" s="42" t="s">
+      <c r="H37" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="66" t="s">
+      <c r="I37" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="B38" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D38" s="65" t="s">
+      <c r="B38" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E38" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E38" s="50" t="s">
+      <c r="F38" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F38" s="49" t="s">
+      <c r="G38" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G38" s="42" t="s">
+      <c r="H38" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="H38" s="66" t="s">
+      <c r="I38" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="B39" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D39" s="65" t="s">
+      <c r="B39" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E39" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E39" s="50" t="s">
+      <c r="F39" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F39" s="49" t="s">
+      <c r="G39" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="42" t="s">
+      <c r="H39" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H39" s="66" t="s">
+      <c r="I39" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="B40" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D40" s="65" t="s">
+      <c r="B40" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E40" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E40" s="50" t="s">
+      <c r="F40" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="49" t="s">
+      <c r="G40" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G40" s="42" t="s">
+      <c r="H40" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="H40" s="66" t="s">
+      <c r="I40" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D41" s="47" t="s">
+      <c r="B41" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E41" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="43" t="s">
+      <c r="F41" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="G41" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G41" s="42" t="s">
+      <c r="H41" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H41" s="66" t="s">
+      <c r="I41" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="64" t="s">
         <v>206</v>
       </c>
-      <c r="B42" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D42" s="47" t="s">
+      <c r="B42" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E42" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="E42" s="43" t="s">
+      <c r="F42" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F42" s="48" t="s">
+      <c r="G42" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G42" s="42" t="s">
+      <c r="H42" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="H42" s="66" t="s">
+      <c r="I42" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="B43" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D43" s="47" t="s">
+      <c r="B43" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E43" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="43" t="s">
+      <c r="F43" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F43" s="48" t="s">
+      <c r="G43" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="42" t="s">
+      <c r="H43" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="H43" s="66" t="s">
+      <c r="I43" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="B44" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D44" s="47" t="s">
+      <c r="B44" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E44" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="E44" s="43" t="s">
+      <c r="F44" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F44" s="48" t="s">
+      <c r="G44" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G44" s="42" t="s">
+      <c r="H44" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="66" t="s">
+      <c r="I44" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="B45" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D45" s="47" t="s">
+      <c r="B45" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E45" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="E45" s="43" t="s">
+      <c r="F45" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F45" s="48" t="s">
+      <c r="G45" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G45" s="42" t="s">
+      <c r="H45" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="H45" s="66" t="s">
+      <c r="I45" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="64" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D46" s="47" t="s">
+      <c r="B46" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E46" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="E46" s="43" t="s">
+      <c r="F46" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="G46" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G46" s="42" t="s">
+      <c r="H46" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="H46" s="66" t="s">
+      <c r="I46" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="B47" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D47" s="65" t="s">
+      <c r="B47" s="47" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E47" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E47" s="50" t="s">
+      <c r="F47" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F47" s="48" t="s">
+      <c r="G47" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G47" s="42" t="s">
+      <c r="H47" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="66" t="s">
+      <c r="I47" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="B48" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D48" s="65" t="s">
+      <c r="B48" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E48" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="F48" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F48" s="48" t="s">
+      <c r="G48" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G48" s="42" t="s">
+      <c r="H48" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="H48" s="66" t="s">
+      <c r="I48" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="B49" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D49" s="65" t="s">
+      <c r="B49" s="47" t="s">
+        <v>267</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E49" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E49" s="50" t="s">
+      <c r="F49" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F49" s="48" t="s">
+      <c r="G49" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G49" s="42" t="s">
+      <c r="H49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="H49" s="66" t="s">
+      <c r="I49" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="B50" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D50" s="47" t="s">
+      <c r="B50" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E50" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="E50" s="51" t="s">
+      <c r="F50" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64" t="s">
+      <c r="G50" s="64"/>
+      <c r="H50" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="H50" s="66" t="s">
+      <c r="I50" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="B51" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D51" s="47" t="s">
+      <c r="B51" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E51" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="E51" s="51" t="s">
+      <c r="F51" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F51" s="64"/>
-      <c r="G51" s="64" t="s">
+      <c r="G51" s="64"/>
+      <c r="H51" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H51" s="66" t="s">
+      <c r="I51" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="B52" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="45">
-        <v>45170</v>
-      </c>
-      <c r="D52" s="47" t="s">
+      <c r="B52" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="45">
+        <v>45170</v>
+      </c>
+      <c r="E52" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="E52" s="51" t="s">
+      <c r="F52" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F52" s="64"/>
-      <c r="G52" s="64" t="s">
+      <c r="G52" s="64"/>
+      <c r="H52" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="66" t="s">
+      <c r="I52" s="66" t="s">
         <v>159</v>
       </c>
     </row>
